--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2020_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2020_atacama.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:10</t>
+    <t xml:space="preserve">2026-09-24 01:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -681,13 +681,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
@@ -704,13 +704,13 @@
         <v>9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="10">
@@ -730,10 +730,10 @@
         <v>-0.12</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="11">
@@ -744,7 +744,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>9</v>
@@ -753,7 +753,7 @@
         <v>0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.03</v>
@@ -799,10 +799,10 @@
         <v>-0.2</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="14">
@@ -822,10 +822,10 @@
         <v>0.18</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="15">
@@ -845,7 +845,7 @@
         <v>-0.1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.07</v>
